--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,6 +790,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123905633</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97371</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>1 km OSO om vägbron S om Ertsjärv, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>816488</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7401183</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010 - kompletteringar.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>körväg i skog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lennart Stenberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
         </is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>123905633</v>
       </c>
       <c r="B3" t="n">
-        <v>97371</v>
+        <v>97373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>95526</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>816486.49356621</v>
+        <v>816486</v>
       </c>
       <c r="R2" t="n">
-        <v>7401283.257591287</v>
+        <v>7401283</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -744,19 +739,9 @@
           <t>2000-08-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
+        <v>97906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97906</v>
+        <v>97907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97910</v>
+        <v>97916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97916</v>
+        <v>97919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97919</v>
+        <v>97924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37905-2024 artfynd.xlsx
+++ b/artfynd/A 37905-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109193507</v>
       </c>
       <c r="B2" t="n">
-        <v>97924</v>
+        <v>97926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
